--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -823,151 +823,160 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,1</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0.9880,0.0021,0.0035,0.0010</t>
   </si>
   <si>
-    <t>0.1042,0.0017,0.0039,0.9718</t>
+    <t>0.1046,0.0017,0.0039,0.9717</t>
   </si>
   <si>
     <t>0.9759,0.0034,0.0021,0.0134</t>
   </si>
   <si>
-    <t>0.6595,0.0025,0.0068,0.4015</t>
-  </si>
-  <si>
-    <t>0.9845,0.0109,0.0033,0.0012</t>
-  </si>
-  <si>
-    <t>0.9658,0.0274,0.0041,0.0015</t>
-  </si>
-  <si>
-    <t>0.9838,0.0068,0.0042,0.0010</t>
-  </si>
-  <si>
-    <t>0.9877,0.0042,0.0032,0.0010</t>
-  </si>
-  <si>
-    <t>0.9848,0.0171,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9692,0.0220,0.0042,0.0016</t>
+    <t>0.6606,0.0025,0.0067,0.4004</t>
+  </si>
+  <si>
+    <t>0.9846,0.0109,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.9660,0.0274,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.9839,0.0068,0.0042,0.0010</t>
+  </si>
+  <si>
+    <t>0.9878,0.0042,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.9849,0.0171,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9693,0.0220,0.0042,0.0016</t>
   </si>
   <si>
     <t>0.9802,0.0068,0.0039,0.0021</t>
   </si>
   <si>
-    <t>0.9856,0.0103,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.9142,0.0050,0.0472,0.0048</t>
-  </si>
-  <si>
-    <t>0.0771,0.0171,0.9369,0.0078</t>
-  </si>
-  <si>
-    <t>0.8377,0.0004,0.2579,0.0001</t>
-  </si>
-  <si>
-    <t>0.1992,0.0044,0.8684,0.0012</t>
-  </si>
-  <si>
-    <t>0.9661,0.0008,0.0253,0.0004</t>
-  </si>
-  <si>
-    <t>0.0146,0.9915,0.1024,0.0008</t>
-  </si>
-  <si>
-    <t>0.0462,0.9765,0.0741,0.0017</t>
-  </si>
-  <si>
-    <t>0.8159,0.4701,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.1886,0.8768,0.0851,0.0037</t>
-  </si>
-  <si>
-    <t>0.0062,0.9979,0.0362,0.0000</t>
-  </si>
-  <si>
-    <t>0.6086,0.0009,0.2281,0.0108</t>
-  </si>
-  <si>
-    <t>0.2938,0.0046,0.7902,0.0038</t>
-  </si>
-  <si>
-    <t>0.0612,0.0003,0.9780,0.0001</t>
-  </si>
-  <si>
-    <t>0.0550,0.0024,0.9694,0.0016</t>
-  </si>
-  <si>
-    <t>0.0961,0.0010,0.9447,0.0015</t>
-  </si>
-  <si>
-    <t>0.0942,0.0006,0.9571,0.0005</t>
-  </si>
-  <si>
-    <t>0.0104,0.0006,0.9948,0.0007</t>
-  </si>
-  <si>
-    <t>0.9534,0.0237,0.0160,0.0025</t>
-  </si>
-  <si>
-    <t>0.9734,0.0272,0.0082,0.0031</t>
-  </si>
-  <si>
-    <t>0.0019,0.0003,0.9975,0.0005</t>
-  </si>
-  <si>
-    <t>0.0314,0.5170,0.8366,0.0081</t>
-  </si>
-  <si>
-    <t>0.9439,0.0045,0.0272,0.0013</t>
-  </si>
-  <si>
-    <t>0.9286,0.0023,0.0514,0.0010</t>
-  </si>
-  <si>
-    <t>0.9631,0.0416,0.0076,0.0016</t>
-  </si>
-  <si>
-    <t>0.4017,0.3996,0.1690,0.0028</t>
-  </si>
-  <si>
-    <t>0.0006,0.1701,0.9931,0.0003</t>
+    <t>0.9857,0.0103,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.9146,0.0050,0.0470,0.0048</t>
+  </si>
+  <si>
+    <t>0.0775,0.0172,0.9366,0.0078</t>
+  </si>
+  <si>
+    <t>0.8385,0.0004,0.2566,0.0001</t>
+  </si>
+  <si>
+    <t>0.2000,0.0044,0.8678,0.0012</t>
+  </si>
+  <si>
+    <t>0.9662,0.0008,0.0252,0.0004</t>
+  </si>
+  <si>
+    <t>0.0146,0.9915,0.1019,0.0008</t>
+  </si>
+  <si>
+    <t>0.0462,0.9765,0.0738,0.0017</t>
+  </si>
+  <si>
+    <t>0.8164,0.4695,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.1889,0.8768,0.0847,0.0037</t>
+  </si>
+  <si>
+    <t>0.0062,0.9979,0.0360,0.0000</t>
+  </si>
+  <si>
+    <t>0.6099,0.0009,0.2272,0.0108</t>
+  </si>
+  <si>
+    <t>0.2956,0.0046,0.7887,0.0037</t>
+  </si>
+  <si>
+    <t>0.0615,0.0003,0.9779,0.0001</t>
+  </si>
+  <si>
+    <t>0.0552,0.0024,0.9693,0.0016</t>
+  </si>
+  <si>
+    <t>0.0966,0.0010,0.9444,0.0015</t>
+  </si>
+  <si>
+    <t>0.0946,0.0006,0.9569,0.0005</t>
+  </si>
+  <si>
+    <t>0.0105,0.0006,0.9948,0.0007</t>
+  </si>
+  <si>
+    <t>0.9535,0.0237,0.0159,0.0025</t>
+  </si>
+  <si>
+    <t>0.9735,0.0272,0.0081,0.0031</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.9975,0.0005</t>
+  </si>
+  <si>
+    <t>0.0315,0.5171,0.8361,0.0081</t>
+  </si>
+  <si>
+    <t>0.9442,0.0045,0.0271,0.0013</t>
+  </si>
+  <si>
+    <t>0.9290,0.0023,0.0511,0.0010</t>
+  </si>
+  <si>
+    <t>0.9631,0.0416,0.0075,0.0016</t>
+  </si>
+  <si>
+    <t>0.4025,0.3997,0.1683,0.0028</t>
+  </si>
+  <si>
+    <t>0.0006,0.1702,0.9931,0.0003</t>
   </si>
   <si>
     <t>0.0009,0.0007,0.9991,0.0002</t>
   </si>
   <si>
-    <t>0.0130,0.0070,0.9867,0.0007</t>
-  </si>
-  <si>
-    <t>0.4311,0.0001,0.3914,0.0037</t>
+    <t>0.0130,0.0069,0.9867,0.0007</t>
+  </si>
+  <si>
+    <t>0.4324,0.0001,0.3901,0.0037</t>
   </si>
   <si>
     <t>0.0009,0.0669,0.9952,0.0004</t>
   </si>
   <si>
-    <t>0.0014,0.9761,0.0354,0.0105</t>
+    <t>0.0014,0.9762,0.0353,0.0105</t>
   </si>
   <si>
     <t>0.0010,0.0105,0.9977,0.0006</t>
   </si>
   <si>
-    <t>0.0189,0.0245,0.0056,0.9864</t>
-  </si>
-  <si>
-    <t>0.0006,0.9996,0.0092,0.0003</t>
-  </si>
-  <si>
-    <t>0.0027,0.9984,0.1911,0.0007</t>
-  </si>
-  <si>
-    <t>0.0019,0.9992,0.1160,0.0002</t>
+    <t>0.0189,0.0245,0.0056,0.9863</t>
+  </si>
+  <si>
+    <t>0.0006,0.9996,0.0091,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.9984,0.1907,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.9992,0.1157,0.0002</t>
   </si>
   <si>
     <t>0.0002,0.0035,0.9993,0.0003</t>
@@ -976,55 +985,55 @@
     <t>0.0004,0.0088,0.9988,0.0003</t>
   </si>
   <si>
-    <t>0.0044,0.0008,0.9963,0.0008</t>
-  </si>
-  <si>
-    <t>0.1027,0.0001,0.9695,0.0001</t>
+    <t>0.0045,0.0008,0.9963,0.0008</t>
+  </si>
+  <si>
+    <t>0.1032,0.0001,0.9693,0.0001</t>
   </si>
   <si>
     <t>0.0108,0.0004,0.9957,0.0001</t>
   </si>
   <si>
-    <t>0.0205,0.0057,0.9830,0.0017</t>
-  </si>
-  <si>
-    <t>0.9805,0.0091,0.0059,0.0008</t>
-  </si>
-  <si>
-    <t>0.9506,0.0045,0.0200,0.0013</t>
-  </si>
-  <si>
-    <t>0.9640,0.0230,0.0096,0.0017</t>
-  </si>
-  <si>
-    <t>0.3193,0.0061,0.5759,0.0005</t>
-  </si>
-  <si>
-    <t>0.9498,0.0030,0.0172,0.0013</t>
-  </si>
-  <si>
-    <t>0.9544,0.0108,0.0115,0.0015</t>
-  </si>
-  <si>
-    <t>0.9839,0.0034,0.0056,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9947,0.9839,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0161,0.9997,0.0000</t>
+    <t>0.0206,0.0057,0.9829,0.0017</t>
+  </si>
+  <si>
+    <t>0.9806,0.0091,0.0059,0.0008</t>
+  </si>
+  <si>
+    <t>0.9508,0.0045,0.0199,0.0013</t>
+  </si>
+  <si>
+    <t>0.9641,0.0230,0.0095,0.0017</t>
+  </si>
+  <si>
+    <t>0.3199,0.0061,0.5752,0.0005</t>
+  </si>
+  <si>
+    <t>0.9499,0.0030,0.0171,0.0013</t>
+  </si>
+  <si>
+    <t>0.9546,0.0108,0.0115,0.0015</t>
+  </si>
+  <si>
+    <t>0.9840,0.0034,0.0056,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9947,0.9838,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0160,0.9997,0.0000</t>
   </si>
   <si>
     <t>0.0006,0.0082,0.9985,0.0005</t>
   </si>
   <si>
-    <t>0.0002,0.9522,0.9779,0.0002</t>
+    <t>0.0002,0.9522,0.9778,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.0003,0.9998,0.0001</t>
   </si>
   <si>
-    <t>0.0286,0.9768,0.1395,0.0004</t>
+    <t>0.0286,0.9768,0.1391,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0022,0.0000</t>
@@ -1033,19 +1042,19 @@
     <t>0.9916,0.0008,0.0051,0.0002</t>
   </si>
   <si>
-    <t>0.8287,0.0055,0.1623,0.0016</t>
+    <t>0.8293,0.0055,0.1618,0.0016</t>
   </si>
   <si>
     <t>0.0068,0.0088,0.9933,0.0012</t>
   </si>
   <si>
-    <t>0.0002,0.6273,0.9956,0.0002</t>
+    <t>0.0002,0.6269,0.9956,0.0002</t>
   </si>
   <si>
     <t>0.0002,0.4941,0.9962,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.9979,0.9526,0.0000</t>
+    <t>0.0000,0.9979,0.9525,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9496,0.9949,0.0000</t>
@@ -1060,58 +1069,58 @@
     <t>0.0225,0.0002,0.0007,0.9974</t>
   </si>
   <si>
-    <t>0.0192,0.0009,0.0063,0.9910</t>
-  </si>
-  <si>
-    <t>0.1729,0.0011,0.0051,0.9431</t>
+    <t>0.0193,0.0009,0.0063,0.9910</t>
+  </si>
+  <si>
+    <t>0.1737,0.0011,0.0051,0.9430</t>
   </si>
   <si>
     <t>0.0033,0.0011,0.0094,0.9984</t>
   </si>
   <si>
-    <t>0.0001,0.9666,0.9838,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.1882,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.3141,0.9870,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.1103,0.9981,0.0002</t>
+    <t>0.0001,0.9666,0.9837,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1879,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.3138,0.9870,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.1101,0.9981,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.9677,0.9970,0.0000</t>
   </si>
   <si>
-    <t>0.0005,0.5901,0.9870,0.0001</t>
-  </si>
-  <si>
-    <t>0.9770,0.0247,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.9443,0.0369,0.0085,0.0026</t>
+    <t>0.0005,0.5899,0.9870,0.0001</t>
+  </si>
+  <si>
+    <t>0.9771,0.0247,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.9445,0.0369,0.0085,0.0026</t>
   </si>
   <si>
     <t>0.9846,0.0257,0.0019,0.0002</t>
   </si>
   <si>
-    <t>0.9631,0.0244,0.0048,0.0022</t>
+    <t>0.9632,0.0244,0.0048,0.0022</t>
   </si>
   <si>
     <t>0.9888,0.0041,0.0027,0.0008</t>
   </si>
   <si>
-    <t>0.9900,0.0056,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.9700,0.0040,0.0084,0.0012</t>
-  </si>
-  <si>
-    <t>0.9940,0.0034,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9708,0.0089,0.0046,0.0028</t>
+    <t>0.9901,0.0056,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9701,0.0040,0.0084,0.0012</t>
+  </si>
+  <si>
+    <t>0.9941,0.0034,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9709,0.0089,0.0046,0.0028</t>
   </si>
   <si>
     <t>0.9933,0.0070,0.0015,0.0003</t>
@@ -1123,13 +1132,13 @@
     <t>0.9932,0.0045,0.0013,0.0006</t>
   </si>
   <si>
-    <t>0.9690,0.0177,0.0043,0.0016</t>
+    <t>0.9691,0.0177,0.0043,0.0016</t>
   </si>
   <si>
     <t>0.9978,0.0021,0.0005,0.0001</t>
   </si>
   <si>
-    <t>0.9811,0.0091,0.0031,0.0013</t>
+    <t>0.9812,0.0091,0.0031,0.0013</t>
   </si>
   <si>
     <t>0.9774,0.0075,0.0049,0.0020</t>
@@ -1138,97 +1147,97 @@
     <t>0.0015,0.0001,0.9995,0.0000</t>
   </si>
   <si>
-    <t>0.0555,0.0009,0.9747,0.0008</t>
-  </si>
-  <si>
-    <t>0.9787,0.0001,0.0173,0.0001</t>
-  </si>
-  <si>
-    <t>0.0575,0.0021,0.9677,0.0007</t>
-  </si>
-  <si>
-    <t>0.0091,0.9951,0.0409,0.0004</t>
+    <t>0.0559,0.0009,0.9745,0.0008</t>
+  </si>
+  <si>
+    <t>0.9787,0.0001,0.0172,0.0001</t>
+  </si>
+  <si>
+    <t>0.0577,0.0021,0.9675,0.0007</t>
+  </si>
+  <si>
+    <t>0.0091,0.9951,0.0408,0.0004</t>
   </si>
   <si>
     <t>0.0119,0.9966,0.0089,0.0000</t>
   </si>
   <si>
-    <t>0.8963,0.2730,0.0041,0.0004</t>
-  </si>
-  <si>
-    <t>0.6586,0.5896,0.0177,0.0017</t>
-  </si>
-  <si>
-    <t>0.0521,0.9817,0.0269,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9996,0.0283,0.0001</t>
-  </si>
-  <si>
-    <t>0.9653,0.0376,0.0095,0.0018</t>
-  </si>
-  <si>
-    <t>0.5084,0.0096,0.4535,0.0155</t>
-  </si>
-  <si>
-    <t>0.1502,0.0047,0.8960,0.0019</t>
-  </si>
-  <si>
-    <t>0.8490,0.0053,0.1457,0.0022</t>
-  </si>
-  <si>
-    <t>0.6708,0.0108,0.2954,0.0099</t>
-  </si>
-  <si>
-    <t>0.0043,0.1210,0.6114,0.7740</t>
-  </si>
-  <si>
-    <t>0.0018,0.9990,0.0615,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9995,0.0237,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.9945,0.0469,0.0239</t>
-  </si>
-  <si>
-    <t>0.0004,0.9969,0.7465,0.0003</t>
-  </si>
-  <si>
-    <t>0.1714,0.9005,0.0595,0.0006</t>
-  </si>
-  <si>
-    <t>0.9655,0.0331,0.0090,0.0026</t>
-  </si>
-  <si>
-    <t>0.9237,0.0843,0.0153,0.0039</t>
-  </si>
-  <si>
-    <t>0.9924,0.0020,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9861,0.0115,0.0029,0.0016</t>
-  </si>
-  <si>
-    <t>0.9671,0.0116,0.0048,0.0047</t>
+    <t>0.8966,0.2725,0.0041,0.0004</t>
+  </si>
+  <si>
+    <t>0.6590,0.5893,0.0177,0.0017</t>
+  </si>
+  <si>
+    <t>0.0521,0.9817,0.0268,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9996,0.0282,0.0001</t>
+  </si>
+  <si>
+    <t>0.9653,0.0375,0.0095,0.0018</t>
+  </si>
+  <si>
+    <t>0.5101,0.0097,0.4518,0.0155</t>
+  </si>
+  <si>
+    <t>0.1509,0.0047,0.8955,0.0019</t>
+  </si>
+  <si>
+    <t>0.8497,0.0053,0.1449,0.0022</t>
+  </si>
+  <si>
+    <t>0.6725,0.0108,0.2937,0.0098</t>
+  </si>
+  <si>
+    <t>0.0043,0.1213,0.6107,0.7742</t>
+  </si>
+  <si>
+    <t>0.0018,0.9990,0.0613,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.9995,0.0236,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.9945,0.0468,0.0238</t>
+  </si>
+  <si>
+    <t>0.0004,0.9969,0.7459,0.0003</t>
+  </si>
+  <si>
+    <t>0.1716,0.9005,0.0593,0.0006</t>
+  </si>
+  <si>
+    <t>0.9656,0.0331,0.0090,0.0026</t>
+  </si>
+  <si>
+    <t>0.9238,0.0843,0.0152,0.0038</t>
+  </si>
+  <si>
+    <t>0.9925,0.0020,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9861,0.0114,0.0029,0.0016</t>
+  </si>
+  <si>
+    <t>0.9672,0.0116,0.0048,0.0047</t>
   </si>
   <si>
     <t>0.9824,0.0054,0.0054,0.0017</t>
   </si>
   <si>
-    <t>0.9973,0.0011,0.0006,0.0003</t>
+    <t>0.9974,0.0011,0.0006,0.0003</t>
   </si>
   <si>
     <t>0.9786,0.0066,0.0052,0.0021</t>
   </si>
   <si>
-    <t>0.9594,0.0082,0.0068,0.0041</t>
-  </si>
-  <si>
-    <t>0.9698,0.0052,0.0079,0.0023</t>
-  </si>
-  <si>
-    <t>0.0003,0.5794,0.9921,0.0001</t>
+    <t>0.9596,0.0082,0.0068,0.0040</t>
+  </si>
+  <si>
+    <t>0.9700,0.0052,0.0079,0.0023</t>
+  </si>
+  <si>
+    <t>0.0003,0.5795,0.9921,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.0321,0.9991,0.0000</t>
@@ -1237,22 +1246,22 @@
     <t>0.0002,0.0047,0.9995,0.0001</t>
   </si>
   <si>
-    <t>0.0040,0.0029,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.9834,0.0004,0.0060,0.0006</t>
-  </si>
-  <si>
-    <t>0.9122,0.0255,0.0402,0.0062</t>
-  </si>
-  <si>
-    <t>0.4089,0.0002,0.6475,0.0010</t>
-  </si>
-  <si>
-    <t>0.9613,0.0012,0.0216,0.0008</t>
-  </si>
-  <si>
-    <t>0.0499,0.0006,0.0062,0.9706</t>
+    <t>0.0040,0.0029,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.9835,0.0004,0.0059,0.0006</t>
+  </si>
+  <si>
+    <t>0.9124,0.0255,0.0400,0.0062</t>
+  </si>
+  <si>
+    <t>0.4099,0.0002,0.6467,0.0010</t>
+  </si>
+  <si>
+    <t>0.9614,0.0012,0.0215,0.0008</t>
+  </si>
+  <si>
+    <t>0.0502,0.0006,0.0062,0.9706</t>
   </si>
   <si>
     <t>0.0003,0.0002,0.0025,0.9999</t>
@@ -1261,112 +1270,112 @@
     <t>0.0009,0.0001,0.0011,0.9999</t>
   </si>
   <si>
-    <t>0.0331,0.0006,0.0049,0.9924</t>
-  </si>
-  <si>
-    <t>0.0000,0.9640,0.9903,0.0001</t>
-  </si>
-  <si>
-    <t>0.9483,0.0024,0.0140,0.0018</t>
-  </si>
-  <si>
-    <t>0.4288,0.4813,0.1115,0.0151</t>
+    <t>0.0333,0.0006,0.0049,0.9923</t>
+  </si>
+  <si>
+    <t>0.0000,0.9640,0.9902,0.0001</t>
+  </si>
+  <si>
+    <t>0.9486,0.0024,0.0140,0.0017</t>
+  </si>
+  <si>
+    <t>0.4295,0.4813,0.1111,0.0151</t>
   </si>
   <si>
     <t>0.9896,0.0022,0.0028,0.0011</t>
   </si>
   <si>
-    <t>0.5407,0.5309,0.0466,0.0026</t>
-  </si>
-  <si>
-    <t>0.9877,0.0044,0.0029,0.0024</t>
-  </si>
-  <si>
-    <t>0.5535,0.0000,0.5831,0.0000</t>
-  </si>
-  <si>
-    <t>0.5261,0.0000,0.5628,0.0000</t>
+    <t>0.5412,0.5310,0.0464,0.0026</t>
+  </si>
+  <si>
+    <t>0.9878,0.0044,0.0029,0.0024</t>
+  </si>
+  <si>
+    <t>0.5539,0.0000,0.5826,0.0000</t>
+  </si>
+  <si>
+    <t>0.5267,0.0000,0.5620,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9812,0.0004,0.0064,0.0006</t>
+    <t>0.9813,0.0004,0.0064,0.0006</t>
   </si>
   <si>
     <t>0.9875,0.0068,0.0045,0.0010</t>
   </si>
   <si>
-    <t>0.9604,0.0067,0.0221,0.0015</t>
+    <t>0.9605,0.0067,0.0220,0.0015</t>
   </si>
   <si>
     <t>0.9875,0.0027,0.0048,0.0011</t>
   </si>
   <si>
-    <t>0.9802,0.0055,0.0071,0.0016</t>
-  </si>
-  <si>
-    <t>0.7290,0.2667,0.0934,0.0308</t>
-  </si>
-  <si>
-    <t>0.9695,0.0145,0.0132,0.0014</t>
-  </si>
-  <si>
-    <t>0.9859,0.0021,0.0072,0.0006</t>
-  </si>
-  <si>
-    <t>0.9830,0.0142,0.0035,0.0014</t>
-  </si>
-  <si>
-    <t>0.9938,0.0057,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9775,0.0075,0.0055,0.0029</t>
-  </si>
-  <si>
-    <t>0.9766,0.0031,0.0065,0.0024</t>
+    <t>0.9802,0.0055,0.0071,0.0015</t>
+  </si>
+  <si>
+    <t>0.7294,0.2667,0.0931,0.0306</t>
+  </si>
+  <si>
+    <t>0.9696,0.0145,0.0132,0.0014</t>
+  </si>
+  <si>
+    <t>0.9860,0.0021,0.0072,0.0006</t>
+  </si>
+  <si>
+    <t>0.9831,0.0142,0.0035,0.0014</t>
+  </si>
+  <si>
+    <t>0.9939,0.0057,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9775,0.0075,0.0055,0.0028</t>
+  </si>
+  <si>
+    <t>0.9766,0.0032,0.0065,0.0024</t>
   </si>
   <si>
     <t>0.9907,0.0061,0.0020,0.0009</t>
   </si>
   <si>
-    <t>0.9843,0.0102,0.0032,0.0019</t>
-  </si>
-  <si>
-    <t>0.9865,0.0080,0.0023,0.0017</t>
-  </si>
-  <si>
-    <t>0.9673,0.0046,0.0066,0.0053</t>
-  </si>
-  <si>
-    <t>0.9689,0.0425,0.0049,0.0017</t>
-  </si>
-  <si>
-    <t>0.9034,0.1353,0.0170,0.0039</t>
-  </si>
-  <si>
-    <t>0.9861,0.0062,0.0043,0.0008</t>
-  </si>
-  <si>
-    <t>0.9111,0.0273,0.0264,0.0010</t>
-  </si>
-  <si>
-    <t>0.9748,0.0125,0.0071,0.0016</t>
-  </si>
-  <si>
-    <t>0.9822,0.0075,0.0051,0.0013</t>
-  </si>
-  <si>
-    <t>0.9775,0.0032,0.0097,0.0010</t>
-  </si>
-  <si>
-    <t>0.9389,0.0402,0.0141,0.0061</t>
-  </si>
-  <si>
-    <t>0.0193,0.0064,0.9801,0.0003</t>
-  </si>
-  <si>
-    <t>0.9752,0.0134,0.0081,0.0012</t>
+    <t>0.9844,0.0102,0.0032,0.0019</t>
+  </si>
+  <si>
+    <t>0.9865,0.0079,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.9674,0.0046,0.0066,0.0053</t>
+  </si>
+  <si>
+    <t>0.9690,0.0425,0.0049,0.0017</t>
+  </si>
+  <si>
+    <t>0.9036,0.1352,0.0169,0.0039</t>
+  </si>
+  <si>
+    <t>0.9862,0.0062,0.0043,0.0008</t>
+  </si>
+  <si>
+    <t>0.9115,0.0273,0.0263,0.0010</t>
+  </si>
+  <si>
+    <t>0.9749,0.0125,0.0071,0.0016</t>
+  </si>
+  <si>
+    <t>0.9823,0.0075,0.0051,0.0013</t>
+  </si>
+  <si>
+    <t>0.9776,0.0032,0.0097,0.0010</t>
+  </si>
+  <si>
+    <t>0.9391,0.0402,0.0141,0.0061</t>
+  </si>
+  <si>
+    <t>0.0194,0.0064,0.9800,0.0003</t>
+  </si>
+  <si>
+    <t>0.9753,0.0134,0.0081,0.0012</t>
   </si>
   <si>
     <t>0.0002,0.0006,0.9998,0.0000</t>
@@ -1375,10 +1384,10 @@
     <t>0.0004,0.0089,0.9981,0.0014</t>
   </si>
   <si>
-    <t>0.0661,0.0006,0.9521,0.0018</t>
-  </si>
-  <si>
-    <t>0.0048,0.0192,0.9919,0.0007</t>
+    <t>0.0663,0.0006,0.9519,0.0018</t>
+  </si>
+  <si>
+    <t>0.0048,0.0192,0.9918,0.0007</t>
   </si>
   <si>
     <t>0.0014,0.0015,0.9987,0.0002</t>
@@ -1387,70 +1396,70 @@
     <t>0.0018,0.0002,0.9993,0.0000</t>
   </si>
   <si>
-    <t>0.0560,0.0005,0.9788,0.0001</t>
-  </si>
-  <si>
-    <t>0.6881,0.0073,0.3678,0.0014</t>
-  </si>
-  <si>
-    <t>0.7411,0.0023,0.3244,0.0007</t>
-  </si>
-  <si>
-    <t>0.8974,0.0197,0.0608,0.0033</t>
-  </si>
-  <si>
-    <t>0.3838,0.0182,0.6795,0.0080</t>
-  </si>
-  <si>
-    <t>0.0893,0.0621,0.8753,0.0035</t>
-  </si>
-  <si>
-    <t>0.4204,0.0072,0.6390,0.0021</t>
-  </si>
-  <si>
-    <t>0.7143,0.0048,0.2384,0.0093</t>
-  </si>
-  <si>
-    <t>0.9118,0.0162,0.0713,0.0013</t>
-  </si>
-  <si>
-    <t>0.7874,0.3565,0.0138,0.0004</t>
-  </si>
-  <si>
-    <t>0.1948,0.9133,0.0282,0.0003</t>
-  </si>
-  <si>
-    <t>0.6318,0.5507,0.0182,0.0014</t>
-  </si>
-  <si>
-    <t>0.9741,0.0097,0.0077,0.0011</t>
-  </si>
-  <si>
-    <t>0.8452,0.1213,0.0229,0.0027</t>
-  </si>
-  <si>
-    <t>0.9318,0.0304,0.0182,0.0006</t>
-  </si>
-  <si>
-    <t>0.9912,0.0006,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.8469,0.0155,0.1097,0.0100</t>
-  </si>
-  <si>
-    <t>0.5431,0.0019,0.4742,0.0049</t>
-  </si>
-  <si>
-    <t>0.9059,0.0023,0.0518,0.0035</t>
-  </si>
-  <si>
-    <t>0.0401,0.0007,0.9789,0.0013</t>
-  </si>
-  <si>
-    <t>0.2548,0.0006,0.8304,0.0002</t>
-  </si>
-  <si>
-    <t>0.1319,0.0030,0.9001,0.0003</t>
+    <t>0.0562,0.0005,0.9787,0.0001</t>
+  </si>
+  <si>
+    <t>0.6894,0.0073,0.3663,0.0014</t>
+  </si>
+  <si>
+    <t>0.7422,0.0023,0.3231,0.0007</t>
+  </si>
+  <si>
+    <t>0.8976,0.0197,0.0606,0.0033</t>
+  </si>
+  <si>
+    <t>0.3850,0.0182,0.6783,0.0080</t>
+  </si>
+  <si>
+    <t>0.0899,0.0621,0.8746,0.0035</t>
+  </si>
+  <si>
+    <t>0.4219,0.0072,0.6375,0.0021</t>
+  </si>
+  <si>
+    <t>0.7153,0.0048,0.2375,0.0092</t>
+  </si>
+  <si>
+    <t>0.9122,0.0162,0.0708,0.0013</t>
+  </si>
+  <si>
+    <t>0.7876,0.3563,0.0138,0.0004</t>
+  </si>
+  <si>
+    <t>0.1951,0.9132,0.0281,0.0003</t>
+  </si>
+  <si>
+    <t>0.6321,0.5508,0.0181,0.0013</t>
+  </si>
+  <si>
+    <t>0.9742,0.0097,0.0076,0.0011</t>
+  </si>
+  <si>
+    <t>0.8455,0.1214,0.0228,0.0027</t>
+  </si>
+  <si>
+    <t>0.9319,0.0303,0.0181,0.0006</t>
+  </si>
+  <si>
+    <t>0.9913,0.0006,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.8476,0.0154,0.1092,0.0099</t>
+  </si>
+  <si>
+    <t>0.5442,0.0019,0.4731,0.0049</t>
+  </si>
+  <si>
+    <t>0.9063,0.0023,0.0516,0.0035</t>
+  </si>
+  <si>
+    <t>0.0402,0.0007,0.9789,0.0013</t>
+  </si>
+  <si>
+    <t>0.2556,0.0006,0.8298,0.0002</t>
+  </si>
+  <si>
+    <t>0.1324,0.0030,0.8996,0.0003</t>
   </si>
   <si>
     <t>0.0020,0.0050,0.9972,0.0003</t>
@@ -1459,22 +1468,22 @@
     <t>0.0088,0.0014,0.9933,0.0001</t>
   </si>
   <si>
-    <t>0.9798,0.0032,0.0043,0.0020</t>
-  </si>
-  <si>
-    <t>0.9769,0.0138,0.0045,0.0027</t>
-  </si>
-  <si>
-    <t>0.9483,0.0163,0.0071,0.0055</t>
-  </si>
-  <si>
-    <t>0.9919,0.0080,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9361,0.0359,0.0095,0.0045</t>
-  </si>
-  <si>
-    <t>0.9498,0.0292,0.0072,0.0033</t>
+    <t>0.9799,0.0032,0.0043,0.0020</t>
+  </si>
+  <si>
+    <t>0.9769,0.0137,0.0045,0.0026</t>
+  </si>
+  <si>
+    <t>0.9485,0.0163,0.0071,0.0054</t>
+  </si>
+  <si>
+    <t>0.9920,0.0080,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9362,0.0359,0.0095,0.0045</t>
+  </si>
+  <si>
+    <t>0.9500,0.0292,0.0072,0.0033</t>
   </si>
   <si>
     <t>0.9836,0.0126,0.0030,0.0015</t>
@@ -1483,13 +1492,13 @@
     <t>0.9883,0.0032,0.0029,0.0011</t>
   </si>
   <si>
-    <t>0.0365,0.0075,0.9597,0.0022</t>
-  </si>
-  <si>
-    <t>0.3847,0.0283,0.6213,0.0052</t>
-  </si>
-  <si>
-    <t>0.7198,0.0046,0.0965,0.0245</t>
+    <t>0.0367,0.0076,0.9596,0.0022</t>
+  </si>
+  <si>
+    <t>0.3859,0.0284,0.6202,0.0052</t>
+  </si>
+  <si>
+    <t>0.7211,0.0046,0.0961,0.0244</t>
   </si>
   <si>
     <t>0.0004,0.0006,0.9996,0.0001</t>
@@ -1501,19 +1510,19 @@
     <t>0.0030,0.0201,0.9939,0.0008</t>
   </si>
   <si>
-    <t>0.0158,0.0032,0.9877,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0028,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.2265,0.0109,0.8205,0.0062</t>
-  </si>
-  <si>
-    <t>0.9310,0.0016,0.0526,0.0007</t>
-  </si>
-  <si>
-    <t>0.8121,0.0005,0.0415,0.0162</t>
+    <t>0.0158,0.0032,0.9876,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0028,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.2275,0.0109,0.8197,0.0062</t>
+  </si>
+  <si>
+    <t>0.9313,0.0016,0.0524,0.0007</t>
+  </si>
+  <si>
+    <t>0.8128,0.0005,0.0413,0.0161</t>
   </si>
   <si>
     <t>0.9850,0.0017,0.0061,0.0003</t>
@@ -1525,10 +1534,10 @@
     <t>0.9867,0.0160,0.0021,0.0006</t>
   </si>
   <si>
-    <t>0.9778,0.0194,0.0038,0.0016</t>
-  </si>
-  <si>
-    <t>0.9621,0.0279,0.0078,0.0030</t>
+    <t>0.9779,0.0194,0.0038,0.0016</t>
+  </si>
+  <si>
+    <t>0.9622,0.0279,0.0078,0.0030</t>
   </si>
   <si>
     <t>0.9879,0.0030,0.0029,0.0011</t>
@@ -1537,13 +1546,13 @@
     <t>0.9678,0.0302,0.0047,0.0017</t>
   </si>
   <si>
-    <t>0.9736,0.0157,0.0038,0.0022</t>
-  </si>
-  <si>
-    <t>0.9435,0.0167,0.0108,0.0026</t>
-  </si>
-  <si>
-    <t>0.0088,0.0134,0.9877,0.0008</t>
+    <t>0.9737,0.0157,0.0038,0.0022</t>
+  </si>
+  <si>
+    <t>0.9437,0.0167,0.0108,0.0026</t>
+  </si>
+  <si>
+    <t>0.0089,0.0134,0.9877,0.0008</t>
   </si>
   <si>
     <t>0.0008,0.0014,0.9993,0.0000</t>
@@ -1552,37 +1561,37 @@
     <t>0.0011,0.0009,0.9991,0.0000</t>
   </si>
   <si>
-    <t>0.0294,0.0140,0.9680,0.0012</t>
-  </si>
-  <si>
-    <t>0.0172,0.0004,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.7888,0.0103,0.0810,0.0247</t>
-  </si>
-  <si>
-    <t>0.1834,0.0095,0.8207,0.0102</t>
+    <t>0.0295,0.0140,0.9679,0.0012</t>
+  </si>
+  <si>
+    <t>0.0173,0.0004,0.9929,0.0001</t>
+  </si>
+  <si>
+    <t>0.7894,0.0103,0.0808,0.0246</t>
+  </si>
+  <si>
+    <t>0.1845,0.0095,0.8196,0.0102</t>
   </si>
   <si>
     <t>0.0006,0.0006,0.9993,0.0003</t>
   </si>
   <si>
-    <t>0.9834,0.0018,0.0020,0.0046</t>
+    <t>0.9835,0.0018,0.0020,0.0046</t>
   </si>
   <si>
     <t>0.0134,0.0001,0.0004,0.9989</t>
   </si>
   <si>
-    <t>0.0486,0.0004,0.0021,0.9901</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.0035,0.9996</t>
+    <t>0.0487,0.0004,0.0021,0.9900</t>
+  </si>
+  <si>
+    <t>0.0021,0.0001,0.0035,0.9996</t>
   </si>
   <si>
     <t>0.0012,0.0004,0.0016,0.9998</t>
   </si>
   <si>
-    <t>0.8830,0.0033,0.0061,0.0870</t>
+    <t>0.8833,0.0033,0.0061,0.0866</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1982,7 +1991,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,7 +2005,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,7 +2019,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,7 +2033,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2038,7 +2047,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2052,7 +2061,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,7 +2075,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2080,7 +2089,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2094,7 +2103,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2108,7 +2117,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2122,7 +2131,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2136,7 +2145,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,7 +2159,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,7 +2173,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,7 +2187,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2192,7 +2201,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,7 +2215,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,7 +2229,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,7 +2243,7 @@
         <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,7 +2257,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,7 +2271,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2276,7 +2285,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,7 +2299,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,7 +2313,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,7 +2327,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,7 +2341,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,7 +2355,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,7 +2369,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2374,7 +2383,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,7 +2397,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,7 +2411,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,7 +2425,7 @@
         <v>268</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2430,7 +2439,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2444,7 +2453,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,7 +2467,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2469,10 +2478,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,7 +2495,7 @@
         <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,7 +2509,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,7 +2523,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2525,10 +2534,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,7 +2551,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,7 +2565,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,7 +2579,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,7 +2593,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,7 +2607,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,7 +2621,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,7 +2635,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,7 +2649,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,7 +2663,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,7 +2677,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,7 +2691,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,7 +2705,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,7 +2719,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,7 +2733,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2738,7 +2747,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2752,7 +2761,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,7 +2775,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2780,7 +2789,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2794,7 +2803,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,7 +2817,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,7 +2831,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,7 +2845,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,7 +2859,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,7 +2873,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,7 +2887,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,7 +2901,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,7 +2915,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2920,7 +2929,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,7 +2943,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,7 +2957,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,7 +2971,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,7 +2985,7 @@
         <v>266</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,7 +2999,7 @@
         <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,7 +3013,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3018,7 +3027,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3032,7 +3041,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3046,7 +3055,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3060,7 +3069,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3074,7 +3083,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,7 +3097,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,7 +3111,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,7 +3125,7 @@
         <v>266</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,7 +3139,7 @@
         <v>266</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,7 +3153,7 @@
         <v>266</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,7 +3167,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,7 +3181,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,7 +3195,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,7 +3209,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3214,7 +3223,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3228,7 +3237,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3242,7 +3251,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3256,7 +3265,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3270,7 +3279,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3284,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3298,7 +3307,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3312,7 +3321,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3326,7 +3335,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3340,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3354,7 +3363,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3368,7 +3377,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,7 +3391,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,7 +3405,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,7 +3419,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,7 +3433,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3438,7 +3447,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,7 +3461,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,7 +3475,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,7 +3489,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,7 +3503,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3505,10 +3514,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,7 +3531,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,7 +3545,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3550,7 +3559,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,7 +3573,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,7 +3587,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3592,7 +3601,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,7 +3615,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3617,10 +3626,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,7 +3643,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,7 +3657,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,7 +3671,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,7 +3685,7 @@
         <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,7 +3699,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,7 +3713,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,7 +3727,7 @@
         <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3732,7 +3741,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3746,7 +3755,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,7 +3769,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3774,7 +3783,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3788,7 +3797,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,7 +3811,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3816,7 +3825,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3830,7 +3839,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,7 +3853,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,7 +3867,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,7 +3881,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,7 +3895,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3900,7 +3909,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,7 +3923,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3928,7 +3937,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3942,7 +3951,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3956,7 +3965,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,7 +3979,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,7 +3993,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3998,7 +4007,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,7 +4021,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4026,7 +4035,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4037,10 +4046,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,7 +4063,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4065,10 +4074,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4082,7 +4091,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4093,10 +4102,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4107,10 +4116,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,7 +4133,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4138,7 +4147,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4152,7 +4161,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,7 +4175,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4180,7 +4189,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4194,7 +4203,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,7 +4217,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4222,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4236,7 +4245,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,7 +4259,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4264,7 +4273,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4278,7 +4287,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4292,7 +4301,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4306,7 +4315,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,7 +4329,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4334,7 +4343,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4348,7 +4357,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,7 +4371,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,7 +4385,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,7 +4399,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4404,7 +4413,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,7 +4427,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,7 +4441,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4446,7 +4455,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4460,7 +4469,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,7 +4483,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,7 +4497,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,7 +4511,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,7 +4525,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,7 +4539,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,7 +4553,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,7 +4567,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,7 +4581,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,7 +4595,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,7 +4609,7 @@
         <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,7 +4623,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4628,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,7 +4651,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,7 +4665,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,7 +4679,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4684,7 +4693,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,7 +4707,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,7 +4721,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,7 +4735,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4737,10 +4746,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4754,7 +4763,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,7 +4777,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,7 +4791,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4796,7 +4805,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4810,7 +4819,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,7 +4833,7 @@
         <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,7 +4847,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,7 +4861,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,7 +4875,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,7 +4889,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,7 +4903,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,7 +4917,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,7 +4931,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4936,7 +4945,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4950,7 +4959,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4964,7 +4973,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4978,7 +4987,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4992,7 +5001,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5006,7 +5015,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,7 +5029,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,7 +5043,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,7 +5057,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,7 +5071,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,7 +5085,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,7 +5099,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,7 +5113,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,7 +5127,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,7 +5141,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,7 +5155,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,7 +5169,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,7 +5183,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5188,7 +5197,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5202,7 +5211,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5216,7 +5225,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5230,7 +5239,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,7 +5253,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5258,7 +5267,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5272,7 +5281,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,7 +5295,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5300,7 +5309,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5314,7 +5323,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5328,7 +5337,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,7 +5351,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,7 +5365,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,7 +5379,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,7 +5393,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,7 +5407,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5412,7 +5421,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,7 +5435,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,7 +5449,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,7 +5463,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5468,7 +5477,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5482,7 +5491,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5496,7 +5505,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,7 +5519,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5524,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
